--- a/backend/data/metrics.xlsx
+++ b/backend/data/metrics.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="216">
   <si>
     <t>ID</t>
   </si>
@@ -773,6 +773,24 @@
   </si>
   <si>
     <t>4896.56</t>
+  </si>
+  <si>
+    <t>1af170c3-4c0e-41d4-8970-d06e4c082be6</t>
+  </si>
+  <si>
+    <t>2025-12-13T14:30:08.040Z</t>
+  </si>
+  <si>
+    <t>e98d7f81-5ba6-4f97-a20a-cac0a863778f</t>
+  </si>
+  <si>
+    <t>5.31</t>
+  </si>
+  <si>
+    <t>23.89</t>
+  </si>
+  <si>
+    <t>5068.98</t>
   </si>
 </sst>
 </file>
@@ -1169,7 +1187,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T27"/>
+  <dimension ref="A1:T28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -2866,6 +2884,68 @@
         <v>27</v>
       </c>
     </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F28" s="2">
+        <v>7</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H28" s="2">
+        <v>200</v>
+      </c>
+      <c r="I28" s="2">
+        <v>2824</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="K28" s="2">
+        <v>15</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="P28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="2">
+        <v>0</v>
+      </c>
+      <c r="R28" s="2">
+        <v>35</v>
+      </c>
+      <c r="S28" s="2">
+        <v>97</v>
+      </c>
+      <c r="T28" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
